--- a/buecher.xlsx
+++ b/buecher.xlsx
@@ -441,22 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9783791</t>
+          <t>123456</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Das doppelte Lottchen</t>
+          <t>Werther</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Erich Kästner</t>
+          <t>Goethe</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1796</t>
         </is>
       </c>
     </row>
